--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-06-2025.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
